--- a/public/report_templates/caja/reportes/vchCobranza.xlsx
+++ b/public/report_templates/caja/reportes/vchCobranza.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredipymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F644AC04-B7F9-43B7-8085-582695B334BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9400EBC6-2D9C-4A55-AD0C-35FD593CE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchCobranza" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -89,10 +89,7 @@
     <t>(datos_cuota)</t>
   </si>
   <si>
-    <t>GRUPO CREDIPYME</t>
-  </si>
-  <si>
-    <t>RUC: 20611432616</t>
+    <t>CREDIPYME HUANCA SAC</t>
   </si>
 </sst>
 </file>
@@ -248,29 +245,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -597,25 +594,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -623,27 +618,27 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="20"/>
+      <c r="C7" s="17"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -659,10 +654,10 @@
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="15"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="9" t="s">
         <v>3</v>
       </c>
@@ -682,10 +677,10 @@
       <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="19"/>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
@@ -696,42 +691,47 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
@@ -740,11 +740,6 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/public/report_templates/caja/reportes/vchCobranza.xlsx
+++ b/public/report_templates/caja/reportes/vchCobranza.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9400EBC6-2D9C-4A55-AD0C-35FD593CE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C724513-A2B6-4722-A52A-814025ABFC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchCobranza" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -89,7 +89,10 @@
     <t>(datos_cuota)</t>
   </si>
   <si>
-    <t>CREDIPYME HUANCA SAC</t>
+    <t>RUC: 20614827239</t>
+  </si>
+  <si>
+    <t>CREDIPYME HUANCA S.A.C</t>
   </si>
 </sst>
 </file>
@@ -245,9 +248,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -255,19 +267,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -594,23 +597,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -618,27 +623,27 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="20"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -654,10 +659,10 @@
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="9" t="s">
         <v>3</v>
       </c>
@@ -677,10 +682,10 @@
       <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="11" t="s">
         <v>14</v>
       </c>
@@ -691,47 +696,42 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
@@ -740,6 +740,11 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.27559055118110237" right="0" top="0" bottom="0" header="0" footer="0"/>
